--- a/docs/contact-form-app_FT CJ.xlsx
+++ b/docs/contact-form-app_FT CJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\満明\03_ライフプラン情報\05_プログラミング教室\13_確認テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E76CCB8-569A-45B7-A3B9-25DEF61FBA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDBE930-6B9D-4A9F-A7F4-319053345E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37650" yWindow="-9870" windowWidth="29930" windowHeight="17850" xr2:uid="{136015F8-773E-4B2E-B024-80686A71548B}"/>
+    <workbookView xWindow="27390" yWindow="-10450" windowWidth="27830" windowHeight="18430" xr2:uid="{136015F8-773E-4B2E-B024-80686A71548B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="121">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -226,15 +226,6 @@
   </si>
   <si>
     <t>タグ名を変更して「更新」ボタンを押す</t>
-  </si>
-  <si>
-    <t>バリデーション通過時→タグ名が更新されタグ一覧に反映され、/admin にリダイレクト
-バリデーション失敗時→エラーメッセージが編集ページの入力フォーム下に赤文字で表示される
-name必須/&lt;=50/ユニーク（自身の現在名は許可）
-エラーメッセージ:
- a. 未入力の場合：タグ名を入力してください
- b. 50文字を超えた場合：タグ名は50文字以内で入力してください
- c. 重複している場合：そのタグ名は既に使用されています</t>
   </si>
   <si>
     <t>「戻る」ボタンを押す</t>
@@ -737,12 +728,76 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>変更履歴</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリデーション通過時→タグ名が更新されタグ一覧に反映され、/admin にリダイレクト
+バリデーション失敗時→エラーメッセージが編集ページの入力フォーム下に赤文字で表示される
+name必須/&lt;=50/ユニーク（自身の現在名は許可）
+エラーメッセージ:
+ a. 未入力の場合：タグ名を入力してください
+ b. 50文字を超えた場合：タグ名は50文字以内で入力してください
+ c. 重複している場合：そのタグ名は既に使用されています</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（自身の現在名は許可）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>何もデータを変更せずに更新
+→/admin にリダイレクトを確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(テスト漏れ追記)</t>
+    </r>
+    <rPh sb="36" eb="37">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ツイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト漏れを追記し、確認実施し完了。</t>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -764,6 +819,14 @@
       <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -857,7 +920,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -898,15 +961,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -914,6 +968,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1230,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F2213A-4265-49B1-B69E-052A90A76419}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.796875" customWidth="1"/>
@@ -1255,31 +1315,31 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D4" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D5" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.45">
@@ -1290,7 +1350,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
@@ -1299,7 +1359,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>4</v>
@@ -1319,37 +1379,37 @@
       <c r="C7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>115</v>
+      <c r="D7" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="H7" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I7" s="12">
         <v>46218</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
       <c r="B8" s="8">
-        <f t="shared" ref="B8:B45" si="0">ROW()-2</f>
+        <f t="shared" ref="B8:B46" si="0">ROW()-2</f>
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="17"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="6" t="s">
         <v>11</v>
       </c>
@@ -1357,16 +1417,16 @@
         <v>12</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I8" s="12">
         <v>46218</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
@@ -1377,7 +1437,7 @@
       <c r="C9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="17"/>
+      <c r="D9" s="14"/>
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
@@ -1385,16 +1445,16 @@
         <v>14</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I9" s="12">
         <v>46218</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" ht="270" x14ac:dyDescent="0.45">
@@ -1405,24 +1465,24 @@
       <c r="C10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I10" s="12">
         <v>46218</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" ht="90" x14ac:dyDescent="0.45">
@@ -1433,8 +1493,8 @@
       <c r="C11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>62</v>
+      <c r="D11" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -1443,16 +1503,16 @@
         <v>17</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I11" s="12">
         <v>46218</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.45">
@@ -1463,7 +1523,7 @@
       <c r="C12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="17"/>
+      <c r="D12" s="14"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
@@ -1471,16 +1531,16 @@
         <v>19</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I12" s="12">
         <v>46218</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1491,7 +1551,7 @@
       <c r="C13" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="18"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="6" t="s">
         <v>20</v>
       </c>
@@ -1500,13 +1560,13 @@
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I13" s="12">
         <v>46218</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.45">
@@ -1517,8 +1577,8 @@
       <c r="C14" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>63</v>
+      <c r="D14" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>22</v>
@@ -1527,16 +1587,16 @@
         <v>23</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I14" s="12">
         <v>46218</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1547,7 +1607,7 @@
       <c r="C15" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="18"/>
+      <c r="D15" s="15"/>
       <c r="E15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1555,16 +1615,16 @@
         <v>25</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" s="12">
         <v>46218</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.45">
@@ -1575,26 +1635,26 @@
       <c r="C16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>64</v>
+      <c r="D16" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="12">
         <v>46218</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="2:10" s="4" customFormat="1" ht="234" x14ac:dyDescent="0.45">
@@ -1605,24 +1665,24 @@
       <c r="C17" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="17"/>
+      <c r="D17" s="14"/>
       <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I17" s="12">
         <v>46218</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1633,7 +1693,7 @@
       <c r="C18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="18"/>
+      <c r="D18" s="15"/>
       <c r="E18" s="6" t="s">
         <v>28</v>
       </c>
@@ -1641,16 +1701,16 @@
         <v>29</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I18" s="12">
         <v>46218</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="2:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
@@ -1661,26 +1721,26 @@
       <c r="C19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>65</v>
+      <c r="D19" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="H19" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I19" s="12">
         <v>46218</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:10" s="4" customFormat="1" ht="180" x14ac:dyDescent="0.45">
@@ -1691,7 +1751,7 @@
       <c r="C20" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="17"/>
+      <c r="D20" s="14"/>
       <c r="E20" s="6" t="s">
         <v>31</v>
       </c>
@@ -1699,16 +1759,16 @@
         <v>32</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I20" s="12">
         <v>46219</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1719,7 +1779,7 @@
       <c r="C21" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="6" t="s">
         <v>33</v>
       </c>
@@ -1727,16 +1787,16 @@
         <v>34</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" s="12">
         <v>46219</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:10" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.45">
@@ -1747,8 +1807,8 @@
       <c r="C22" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>90</v>
+      <c r="D22" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>35</v>
@@ -1757,16 +1817,16 @@
         <v>36</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I22" s="12">
         <v>46219</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="2:10" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.45">
@@ -1777,7 +1837,7 @@
       <c r="C23" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="17"/>
+      <c r="D23" s="14"/>
       <c r="E23" s="6" t="s">
         <v>37</v>
       </c>
@@ -1785,16 +1845,16 @@
         <v>38</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I23" s="12">
         <v>46219</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1805,7 +1865,7 @@
       <c r="C24" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="17"/>
+      <c r="D24" s="14"/>
       <c r="E24" s="6" t="s">
         <v>39</v>
       </c>
@@ -1813,16 +1873,16 @@
         <v>40</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I24" s="12">
         <v>46219</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1833,7 +1893,7 @@
       <c r="C25" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="17"/>
+      <c r="D25" s="14"/>
       <c r="E25" s="6" t="s">
         <v>41</v>
       </c>
@@ -1841,16 +1901,16 @@
         <v>42</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I25" s="12">
         <v>46219</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="2:10" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.45">
@@ -1861,7 +1921,7 @@
       <c r="C26" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="17"/>
+      <c r="D26" s="14"/>
       <c r="E26" s="7" t="s">
         <v>43</v>
       </c>
@@ -1883,7 +1943,7 @@
       <c r="C27" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="17"/>
+      <c r="D27" s="14"/>
       <c r="E27" s="6" t="s">
         <v>45</v>
       </c>
@@ -1891,16 +1951,16 @@
         <v>46</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" s="12">
         <v>46219</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -1911,7 +1971,7 @@
       <c r="C28" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="18"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="6" t="s">
         <v>47</v>
       </c>
@@ -1919,16 +1979,16 @@
         <v>48</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I28" s="12">
         <v>46219</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="2:10" s="4" customFormat="1" ht="180" x14ac:dyDescent="0.45">
@@ -1940,28 +2000,28 @@
         <v>5</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="12">
         <v>46219</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
       <c r="B30" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1970,51 +2030,49 @@
         <v>5</v>
       </c>
       <c r="D30" s="14"/>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="15"/>
+      <c r="F30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I30" s="12">
+        <v>46220</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="8">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I30" s="12">
-        <v>46219</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.45">
-      <c r="B31" s="8">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="G31" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I31" s="12">
         <v>46219</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="2:10" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.45">
@@ -2025,26 +2083,24 @@
       <c r="C32" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>67</v>
-      </c>
+      <c r="D32" s="15"/>
       <c r="E32" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I32" s="12">
         <v>46219</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="2:10" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.45">
@@ -2055,27 +2111,29 @@
       <c r="C33" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="17"/>
+      <c r="D33" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="E33" s="6" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I33" s="12">
         <v>46219</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.45">
       <c r="B34" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2083,27 +2141,27 @@
       <c r="C34" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="14"/>
       <c r="E34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I34" s="12">
         <v>46219</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="8">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2111,29 +2169,27 @@
       <c r="C35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="D35" s="15"/>
       <c r="E35" s="6" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I35" s="12">
         <v>46219</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.45">
       <c r="B36" s="8">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2142,23 +2198,25 @@
         <v>5</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="F36" s="6" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I36" s="12">
         <v>46219</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -2166,14 +2224,28 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="C37" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
+      <c r="F37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="12">
+        <v>46219</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="38" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B38" s="8">
@@ -2287,11 +2359,39 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
+    <row r="46" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="8">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C48" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.45">
+      <c r="D49" s="17">
+        <v>46220</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A6:J6" xr:uid="{12F2213A-4265-49B1-B69E-052A90A76419}"/>
-  <mergeCells count="8">
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D32:D34"/>
+  <mergeCells count="9">
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="D33:D35"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="D11:D13"/>
     <mergeCell ref="D14:D15"/>
